--- a/data/input/Additional/returns/1p Returns.xlsx
+++ b/data/input/Additional/returns/1p Returns.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[20/04/26 - 18/07/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[27/04/26 - 25/07/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4555470.16</v>
+        <v>6251827.27</v>
       </c>
       <c r="F3" t="n">
-        <v>1116</v>
+        <v>1535</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1113</v>
+        <v>1532</v>
       </c>
       <c r="J3" t="n">
-        <v>241</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4091860.94</v>
+        <v>5697993.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1814</v>
+        <v>2530</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1830</v>
+        <v>2522</v>
       </c>
       <c r="J4" t="n">
-        <v>366</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2547355.1</v>
+        <v>3489136.68</v>
       </c>
       <c r="F5" t="n">
-        <v>413</v>
+        <v>574</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,10 +589,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>409</v>
+        <v>568</v>
       </c>
       <c r="J5" t="n">
-        <v>87</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2292037.54</v>
+        <v>3139993.48</v>
       </c>
       <c r="F6" t="n">
-        <v>303</v>
+        <v>417</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>301</v>
+        <v>418</v>
       </c>
       <c r="J6" t="n">
-        <v>68</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1807296.09</v>
+        <v>2531146.73</v>
       </c>
       <c r="F7" t="n">
-        <v>409</v>
+        <v>574</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>395</v>
+        <v>558</v>
       </c>
       <c r="J7" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1360749.11</v>
+        <v>1857238.71</v>
       </c>
       <c r="F8" t="n">
-        <v>806</v>
+        <v>1099</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>802</v>
+        <v>1088</v>
       </c>
       <c r="J8" t="n">
-        <v>136</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1265157.62</v>
+        <v>1678334.61</v>
       </c>
       <c r="F9" t="n">
-        <v>538</v>
+        <v>714</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>544</v>
+        <v>708</v>
       </c>
       <c r="J9" t="n">
-        <v>164</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>802450.49</v>
+        <v>1119691.38</v>
       </c>
       <c r="F10" t="n">
-        <v>253</v>
+        <v>355</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -769,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>251</v>
+        <v>356</v>
       </c>
       <c r="J10" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>656173.03</v>
+        <v>857156.2000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>123</v>
+        <v>265</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>122</v>
+        <v>263</v>
       </c>
       <c r="J11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>628936.6900000001</v>
+        <v>832758.6900000001</v>
       </c>
       <c r="F12" t="n">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="J12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>558281.39</v>
+        <v>806123.73</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="J13" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>547790.58</v>
+        <v>796416.47</v>
       </c>
       <c r="F14" t="n">
-        <v>413</v>
+        <v>273</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -913,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>401</v>
+        <v>271</v>
       </c>
       <c r="J14" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>536567.5</v>
+        <v>754788.27</v>
       </c>
       <c r="F15" t="n">
-        <v>185</v>
+        <v>568</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>184</v>
+        <v>568</v>
       </c>
       <c r="J15" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>498594.02</v>
+        <v>682812.71</v>
       </c>
       <c r="F16" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -985,10 +985,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>440181.6</v>
+        <v>603663.72</v>
       </c>
       <c r="F17" t="n">
-        <v>320</v>
+        <v>438</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>321</v>
+        <v>433</v>
       </c>
       <c r="J17" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>329508.12</v>
+        <v>469893.33</v>
       </c>
       <c r="F18" t="n">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="J18" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>320838.28</v>
+        <v>459912</v>
       </c>
       <c r="F19" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1093,16 +1093,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="J19" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>313881.51</v>
+        <v>453381.14</v>
       </c>
       <c r="F20" t="n">
-        <v>98</v>
+        <v>216</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>97</v>
+        <v>218</v>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>267102.58</v>
+        <v>386126.62</v>
       </c>
       <c r="F21" t="n">
-        <v>541</v>
+        <v>797</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>545</v>
+        <v>794</v>
       </c>
       <c r="J21" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>266250.7</v>
+        <v>369111.16</v>
       </c>
       <c r="F22" t="n">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1201,22 +1201,22 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="J22" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>261657.77</v>
+        <v>364696.18</v>
       </c>
       <c r="F23" t="n">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1237,22 +1237,22 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>173</v>
+        <v>278</v>
       </c>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>242033.32</v>
+        <v>338849.1</v>
       </c>
       <c r="F24" t="n">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1273,22 +1273,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="J24" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>239233.62</v>
+        <v>310128.9</v>
       </c>
       <c r="F25" t="n">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1309,22 +1309,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="J25" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>236826.31</v>
+        <v>309411.96</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>204</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222638.16</v>
+        <v>294720.94</v>
       </c>
       <c r="F27" t="n">
         <v>130</v>
@@ -1381,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>216158.49</v>
+        <v>285845.74</v>
       </c>
       <c r="F28" t="n">
-        <v>28</v>
+        <v>523</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1417,22 +1417,22 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>521</v>
       </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>210225.99</v>
+        <v>285712.83</v>
       </c>
       <c r="F29" t="n">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="J29" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>201146.61</v>
+        <v>276660.02</v>
       </c>
       <c r="F30" t="n">
-        <v>368</v>
+        <v>101</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1489,22 +1489,22 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>363</v>
+        <v>102</v>
       </c>
       <c r="J30" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>197527.27</v>
+        <v>273488.83</v>
       </c>
       <c r="F31" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1525,16 +1525,16 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>194187.97</v>
+        <v>270389.85</v>
       </c>
       <c r="F32" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>183638.82</v>
+        <v>254105.68</v>
       </c>
       <c r="F33" t="n">
-        <v>66</v>
+        <v>245</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1597,22 +1597,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="J33" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>183497.53</v>
+        <v>229624.32</v>
       </c>
       <c r="F34" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1633,10 +1633,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="J34" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>181575.71</v>
+        <v>226974.03</v>
       </c>
       <c r="F35" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1669,22 +1669,22 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="J35" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>169374.54</v>
+        <v>220146.78</v>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1705,10 +1705,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="J36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>167832.84</v>
+        <v>219395.46</v>
       </c>
       <c r="F37" t="n">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="J37" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>165749.84</v>
+        <v>210483.53</v>
       </c>
       <c r="F38" t="n">
-        <v>16</v>
+        <v>455</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1777,16 +1777,16 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>449</v>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>155765.08</v>
+        <v>207678.83</v>
       </c>
       <c r="F39" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1813,16 +1813,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="J39" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>155328.84</v>
+        <v>205105.57</v>
       </c>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>153073.42</v>
+        <v>199512.45</v>
       </c>
       <c r="F41" t="n">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="J41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>150159.81</v>
+        <v>194623.69</v>
       </c>
       <c r="F42" t="n">
-        <v>323</v>
+        <v>46</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>322</v>
+        <v>48</v>
       </c>
       <c r="J42" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>135973.53</v>
+        <v>191762.52</v>
       </c>
       <c r="F43" t="n">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>50</v>
+        <v>193</v>
       </c>
       <c r="J43" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>135144.88</v>
+        <v>185635.55</v>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1993,22 +1993,22 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J44" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>133671.09</v>
+        <v>185409.16</v>
       </c>
       <c r="F45" t="n">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2029,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>132994.09</v>
+        <v>185107.65</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
         <v>9</v>
@@ -2074,13 +2074,13 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>128788.79</v>
+        <v>180276.28</v>
       </c>
       <c r="F47" t="n">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2101,22 +2101,22 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="J47" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>120127.98</v>
+        <v>175302.81</v>
       </c>
       <c r="F48" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2137,16 +2137,16 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="J48" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>119133.37</v>
+        <v>171656.72</v>
       </c>
       <c r="F49" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2173,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J49" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>113401.66</v>
+        <v>168833.07</v>
       </c>
       <c r="F50" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2209,16 +2209,16 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="J50" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>111497.36</v>
+        <v>168281.13</v>
       </c>
       <c r="F51" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>108967.53</v>
+        <v>167864.34</v>
       </c>
       <c r="F52" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2281,22 +2281,22 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>104949.97</v>
+        <v>164062.6</v>
       </c>
       <c r="F53" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>104083.82</v>
+        <v>151021.08</v>
       </c>
       <c r="F54" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J54" t="n">
         <v>3</v>
@@ -2362,7 +2362,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>97593.89999999999</v>
+        <v>146832.96</v>
       </c>
       <c r="F55" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2389,22 +2389,22 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>94386.47</v>
+        <v>131342.31</v>
       </c>
       <c r="F56" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2425,16 +2425,16 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="J56" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2449,22 +2449,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>89614.39</v>
+        <v>122267.03</v>
       </c>
       <c r="F57" t="n">
+        <v>23</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>23</v>
+      </c>
+      <c r="J57" t="n">
         <v>9</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>84535.95</v>
+        <v>118133.99</v>
       </c>
       <c r="F58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2497,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>81702.5</v>
+        <v>117514.43</v>
       </c>
       <c r="F59" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2533,16 +2533,16 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>81266.92999999999</v>
+        <v>113691.36</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2569,22 +2569,22 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>81197.39999999999</v>
+        <v>112949.12</v>
       </c>
       <c r="F61" t="n">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2605,16 +2605,16 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="J61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>71679.60000000001</v>
+        <v>110674.54</v>
       </c>
       <c r="F62" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2641,16 +2641,16 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>71679.59999999999</v>
+        <v>102747.46</v>
       </c>
       <c r="F63" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>70211.84</v>
+        <v>102737.94</v>
       </c>
       <c r="F64" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="J64" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>69570.35000000001</v>
+        <v>97622.00999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2749,22 +2749,22 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>65530.44</v>
+        <v>95316.03999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2785,22 +2785,22 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>62847.37</v>
+        <v>93516.10000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2821,22 +2821,22 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J67" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>60821.19</v>
+        <v>91001.66</v>
       </c>
       <c r="F68" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2857,16 +2857,16 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J68" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>58387.29</v>
+        <v>89614.39</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2893,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>57188.93</v>
+        <v>89595.67</v>
       </c>
       <c r="F70" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>55197.4</v>
+        <v>89229.67</v>
       </c>
       <c r="F71" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>54240.7</v>
+        <v>87010.08</v>
       </c>
       <c r="F72" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J72" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53333.91</v>
+        <v>79794.03</v>
       </c>
       <c r="F73" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3037,16 +3037,16 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53142.41</v>
+        <v>79145.72</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3073,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>50226.24</v>
+        <v>77877.97</v>
       </c>
       <c r="F75" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>47258.34</v>
+        <v>74753.44</v>
       </c>
       <c r="F76" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3145,16 +3145,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="J76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>45667.77</v>
+        <v>69477.98</v>
       </c>
       <c r="F77" t="n">
         <v>16</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
         <v>4</v>
@@ -3190,7 +3190,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>44389.78</v>
+        <v>67822.85000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3217,16 +3217,16 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>44045.73</v>
+        <v>64898.24000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3253,16 +3253,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3277,28 +3277,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>43016.13</v>
+        <v>60006.73</v>
       </c>
       <c r="F80" t="n">
+        <v>84</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>84</v>
+      </c>
+      <c r="J80" t="n">
         <v>11</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>10</v>
-      </c>
-      <c r="J80" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>42145.73</v>
+        <v>59905.05</v>
       </c>
       <c r="F81" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
         <v>3</v>
@@ -3334,7 +3334,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>40887.3</v>
+        <v>59505.92</v>
       </c>
       <c r="F82" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="J82" t="n">
         <v>7</v>
@@ -3370,7 +3370,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>39811.87</v>
+        <v>58073.69</v>
       </c>
       <c r="F83" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>38833.11</v>
+        <v>57844.77</v>
       </c>
       <c r="F84" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="J84" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>36603.36</v>
+        <v>56305.75</v>
       </c>
       <c r="F85" t="n">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3469,16 +3469,16 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="J85" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>36475.4</v>
+        <v>54285.65</v>
       </c>
       <c r="F86" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3505,16 +3505,16 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>35617.55</v>
+        <v>53883.05</v>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3541,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>35332.1</v>
+        <v>52193.18</v>
       </c>
       <c r="F88" t="n">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3577,22 +3577,22 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>33871.16</v>
+        <v>52183.97</v>
       </c>
       <c r="F89" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3613,16 +3613,16 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>33558.45</v>
+        <v>50267.03</v>
       </c>
       <c r="F90" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3649,22 +3649,22 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>33545.82</v>
+        <v>47433.86</v>
       </c>
       <c r="F91" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3685,16 +3685,16 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>31902.57</v>
+        <v>47252.57</v>
       </c>
       <c r="F92" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3721,22 +3721,22 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J92" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>31891.48</v>
+        <v>46039.82</v>
       </c>
       <c r="F93" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3757,16 +3757,16 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>30161.02</v>
+        <v>45754.2</v>
       </c>
       <c r="F94" t="n">
         <v>10</v>
@@ -3796,13 +3796,13 @@
         <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>29532.51</v>
+        <v>43797.49</v>
       </c>
       <c r="F95" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3829,22 +3829,22 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>28047.45</v>
+        <v>43359.28</v>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>27739.81</v>
+        <v>41124.52</v>
       </c>
       <c r="F97" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3901,16 +3901,16 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3925,28 +3925,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>23641.52</v>
+        <v>39764.39</v>
       </c>
       <c r="F98" t="n">
+        <v>22</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>21</v>
+      </c>
+      <c r="J98" t="n">
         <v>3</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>3</v>
-      </c>
-      <c r="J98" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>22029.67</v>
+        <v>39738.17</v>
       </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3973,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J99" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>21938.12</v>
+        <v>35617.55</v>
       </c>
       <c r="F100" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J100" t="n">
         <v>3</v>
@@ -4018,13 +4018,13 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>20606.75</v>
+        <v>34502.55</v>
       </c>
       <c r="F101" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4045,16 +4045,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>20545.52</v>
+        <v>31617.49</v>
       </c>
       <c r="F102" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4081,16 +4081,16 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>20330.51</v>
+        <v>30687.27</v>
       </c>
       <c r="F103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J103" t="n">
         <v>1</v>
@@ -4126,13 +4126,13 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>20206.76</v>
+        <v>30500.83</v>
       </c>
       <c r="F104" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4153,16 +4153,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>18550.01</v>
+        <v>28417.51</v>
       </c>
       <c r="F105" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4189,16 +4189,16 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="J105" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>17962.71</v>
+        <v>28047.45</v>
       </c>
       <c r="F106" t="n">
         <v>4</v>
@@ -4228,19 +4228,19 @@
         <v>4</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4249,28 +4249,28 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>17795.76</v>
+        <v>26344.92</v>
       </c>
       <c r="F107" t="n">
+        <v>13</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>13</v>
+      </c>
+      <c r="J107" t="n">
         <v>1</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4285,28 +4285,28 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>16944.9</v>
+        <v>24754.77</v>
       </c>
       <c r="F108" t="n">
+        <v>17</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>18</v>
+      </c>
+      <c r="J108" t="n">
         <v>5</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>5</v>
-      </c>
-      <c r="J108" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>16604.26</v>
+        <v>23641.52</v>
       </c>
       <c r="F109" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4333,10 +4333,10 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>16477.1</v>
+        <v>23593.19</v>
       </c>
       <c r="F110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4369,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>16160.15</v>
+        <v>22877.98</v>
       </c>
       <c r="F111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4405,16 +4405,16 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>15581.39</v>
+        <v>22452.54</v>
       </c>
       <c r="F112" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
         <v>1</v>
@@ -4450,7 +4450,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>13506.78</v>
+        <v>20736.48</v>
       </c>
       <c r="F113" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4477,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J113" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>13216.96</v>
+        <v>19825.44</v>
       </c>
       <c r="F114" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J114" t="n">
         <v>1</v>
@@ -4522,13 +4522,13 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>12605.1</v>
+        <v>19336.42</v>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4549,16 +4549,16 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>12103.42</v>
+        <v>19222.88</v>
       </c>
       <c r="F116" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4585,22 +4585,22 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J116" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>12096.29</v>
+        <v>18958.5</v>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4621,16 +4621,16 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>11355.08</v>
+        <v>18148.34</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J118" t="n">
         <v>1</v>
@@ -4666,7 +4666,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>9597.459999999999</v>
+        <v>17795.76</v>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>8641.530000000001</v>
+        <v>14729.66</v>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4729,22 +4729,22 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>7626.27</v>
+        <v>14088.97</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4765,22 +4765,22 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6862.71</v>
+        <v>13557.62</v>
       </c>
       <c r="F122" t="n">
         <v>2</v>
@@ -4810,7 +4810,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6778.81</v>
+        <v>11694.07</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -4846,7 +4846,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6775.4</v>
+        <v>11522.03</v>
       </c>
       <c r="F124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -4882,13 +4882,13 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6438.98</v>
+        <v>9597.459999999999</v>
       </c>
       <c r="F125" t="n">
         <v>2</v>
@@ -4918,7 +4918,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6184.75</v>
+        <v>9519.469999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4945,16 +4945,16 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6104.5</v>
+        <v>9025.43</v>
       </c>
       <c r="F127" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4981,16 +4981,16 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5716.1</v>
+        <v>7628.22</v>
       </c>
       <c r="F128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5017,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J128" t="n">
         <v>2</v>
@@ -5026,13 +5026,13 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5591.52</v>
+        <v>7626.27</v>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -5062,13 +5062,13 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5590.68</v>
+        <v>7116.110000000001</v>
       </c>
       <c r="F130" t="n">
         <v>3</v>
@@ -5089,22 +5089,22 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5113,28 +5113,28 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5507.63</v>
+        <v>6862.71</v>
       </c>
       <c r="F131" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2</v>
+      </c>
+      <c r="J131" t="n">
         <v>1</v>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5377.95</v>
+        <v>6834.74</v>
       </c>
       <c r="F132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -5161,22 +5161,22 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4744.07</v>
+        <v>6775.4</v>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5197,16 +5197,16 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4744.06</v>
+        <v>6438.98</v>
       </c>
       <c r="F134" t="n">
         <v>2</v>
@@ -5236,13 +5236,13 @@
         <v>2</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3929.65</v>
+        <v>5590.68</v>
       </c>
       <c r="F135" t="n">
         <v>3</v>
@@ -5269,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>1</v>
@@ -5278,7 +5278,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3727.12</v>
+        <v>5590.68</v>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5305,16 +5305,16 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3388.98</v>
+        <v>5416.58</v>
       </c>
       <c r="F137" t="n">
         <v>1</v>
@@ -5350,7 +5350,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5365,34 +5365,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3388.14</v>
+        <v>5082.19</v>
       </c>
       <c r="F138" t="n">
+        <v>3</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>3</v>
+      </c>
+      <c r="J138" t="n">
         <v>2</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>2</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3388.12</v>
+        <v>4744.06</v>
       </c>
       <c r="F139" t="n">
         <v>2</v>
@@ -5422,7 +5422,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5437,28 +5437,28 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2477.97</v>
+        <v>3929.65</v>
       </c>
       <c r="F140" t="n">
+        <v>3</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>3</v>
+      </c>
+      <c r="J140" t="n">
         <v>1</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1863.56</v>
+        <v>3388.98</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
@@ -5494,7 +5494,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1694.07</v>
+        <v>3388.14</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -5530,13 +5530,13 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0CFKZ72N7</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1618.05</v>
+        <v>3007.63</v>
       </c>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -5566,13 +5566,13 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>2477.97</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -5602,7 +5602,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>2011.86</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -5629,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>1</v>
@@ -5638,13 +5638,13 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0C8JDHLX9</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>1990.68</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -5665,16 +5665,16 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1863.56</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -5710,36 +5710,216 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>B0CFKZ72N7</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>1694.07</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>B0GW8VBCBL</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>1618.05</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>2</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>B0BLKCSJ7Z</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1016.1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>B0BLK8DNPD</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>464.02</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>B0C8JDHLX9</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
           <t>Tonor</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>-3007.63</v>
-      </c>
-      <c r="F148" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="n">
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>B0GW8ZQRFK</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
         <v>0</v>
       </c>
     </row>
